--- a/data/trans_orig/P79A4_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A4_2023-Habitat-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>769</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -1867,27 +1867,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
